--- a/ValueSet-ACCESSCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSCKMDiagnosisVS.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSCKMDiagnosisVS.xlsx
@@ -31,13 +31,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSCKMDiagnosisVS</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSCKMDiagnosisVS</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSCKMDiagnosisVS.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSCKMDiagnosisVS.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSCKMDiagnosisVS.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSCKMDiagnosisVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-ACCESSCKMDiagnosisVS.xlsx
+++ b/ValueSet-ACCESSCKMDiagnosisVS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="1409">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,30 +105,6 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>E08.00</t>
-  </si>
-  <si>
-    <t>Diabetes mellitus due to underlying condition with hyperosmolarity without nonketotic hyperglycemic-hyperosmolar coma (NKHHC)</t>
-  </si>
-  <si>
-    <t>E08.01</t>
-  </si>
-  <si>
-    <t>Diabetes mellitus due to underlying condition with hyperosmolarity with coma</t>
-  </si>
-  <si>
-    <t>E08.10</t>
-  </si>
-  <si>
-    <t>Diabetes mellitus due to underlying condition with ketoacidosis without coma</t>
-  </si>
-  <si>
-    <t>E08.11</t>
-  </si>
-  <si>
-    <t>Diabetes mellitus due to underlying condition with ketoacidosis with coma</t>
-  </si>
-  <si>
     <t>E08.21</t>
   </si>
   <si>
@@ -585,12 +561,6 @@
     <t>Diabetes mellitus due to underlying condition with other oral complications</t>
   </si>
   <si>
-    <t>E08.641</t>
-  </si>
-  <si>
-    <t>Diabetes mellitus due to underlying condition with hypoglycemia with coma</t>
-  </si>
-  <si>
     <t>E08.649</t>
   </si>
   <si>
@@ -1137,30 +1107,6 @@
     <t>Drug or chemical induced diabetes mellitus without complications</t>
   </si>
   <si>
-    <t>E11.00</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes mellitus with hyperosmolarity without nonketotic hyperglycemic-hyperosmolar coma (NKHHC)</t>
-  </si>
-  <si>
-    <t>E11.01</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes mellitus with hyperosmolarity with coma</t>
-  </si>
-  <si>
-    <t>E11.10</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes mellitus with ketoacidosis without coma</t>
-  </si>
-  <si>
-    <t>E11.11</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes mellitus with ketoacidosis with coma</t>
-  </si>
-  <si>
     <t>E11.21</t>
   </si>
   <si>
@@ -1617,12 +1563,6 @@
     <t>Type 2 diabetes mellitus with other oral complications</t>
   </si>
   <si>
-    <t>E11.641</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes mellitus with hypoglycemia with coma</t>
-  </si>
-  <si>
     <t>E11.649</t>
   </si>
   <si>
@@ -1659,30 +1599,6 @@
     <t>Type 2 diabetes mellitus without complications in remission</t>
   </si>
   <si>
-    <t>E13.00</t>
-  </si>
-  <si>
-    <t>Other specified diabetes mellitus with hyperosmolarity without nonketotic hyperglycemic-hyperosmolar coma (NKHHC)</t>
-  </si>
-  <si>
-    <t>E13.01</t>
-  </si>
-  <si>
-    <t>Other specified diabetes mellitus with hyperosmolarity with coma</t>
-  </si>
-  <si>
-    <t>E13.10</t>
-  </si>
-  <si>
-    <t>Other specified diabetes mellitus with ketoacidosis without coma</t>
-  </si>
-  <si>
-    <t>E13.11</t>
-  </si>
-  <si>
-    <t>Other specified diabetes mellitus with ketoacidosis with coma</t>
-  </si>
-  <si>
     <t>E13.21</t>
   </si>
   <si>
@@ -2137,12 +2053,6 @@
   </si>
   <si>
     <t>Other specified diabetes mellitus with other oral complications</t>
-  </si>
-  <si>
-    <t>E13.641</t>
-  </si>
-  <si>
-    <t>Other specified diabetes mellitus with hypoglycemia with coma</t>
   </si>
   <si>
     <t>E13.649</t>
@@ -4595,7 +4505,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B691"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -10119,135 +10029,15 @@
         <v>1406</v>
       </c>
       <c r="B690" t="s" s="2">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
+        <v>1407</v>
+      </c>
+      <c r="B691" t="s" s="2">
         <v>1408</v>
-      </c>
-      <c r="B691" t="s" s="2">
-        <v>1409</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="s" s="2">
-        <v>1410</v>
-      </c>
-      <c r="B692" t="s" s="2">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="s" s="2">
-        <v>1412</v>
-      </c>
-      <c r="B693" t="s" s="2">
-        <v>1413</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="s" s="2">
-        <v>1414</v>
-      </c>
-      <c r="B694" t="s" s="2">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="s" s="2">
-        <v>1416</v>
-      </c>
-      <c r="B695" t="s" s="2">
-        <v>1417</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="s" s="2">
-        <v>1418</v>
-      </c>
-      <c r="B696" t="s" s="2">
-        <v>1419</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="s" s="2">
-        <v>1420</v>
-      </c>
-      <c r="B697" t="s" s="2">
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" t="s" s="2">
-        <v>1422</v>
-      </c>
-      <c r="B698" t="s" s="2">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="699">
-      <c r="A699" t="s" s="2">
-        <v>1424</v>
-      </c>
-      <c r="B699" t="s" s="2">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" t="s" s="2">
-        <v>1426</v>
-      </c>
-      <c r="B700" t="s" s="2">
-        <v>1427</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" t="s" s="2">
-        <v>1428</v>
-      </c>
-      <c r="B701" t="s" s="2">
-        <v>1429</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" t="s" s="2">
-        <v>1430</v>
-      </c>
-      <c r="B702" t="s" s="2">
-        <v>1431</v>
-      </c>
-    </row>
-    <row r="703">
-      <c r="A703" t="s" s="2">
-        <v>1432</v>
-      </c>
-      <c r="B703" t="s" s="2">
-        <v>1433</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" t="s" s="2">
-        <v>1434</v>
-      </c>
-      <c r="B704" t="s" s="2">
-        <v>1435</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" t="s" s="2">
-        <v>1436</v>
-      </c>
-      <c r="B705" t="s" s="2">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="s" s="2">
-        <v>1437</v>
-      </c>
-      <c r="B706" t="s" s="2">
-        <v>1438</v>
       </c>
     </row>
   </sheetData>
